--- a/portfolio_media/VEX_Volunteering.xlsx
+++ b/portfolio_media/VEX_Volunteering.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ab1e07f38fe66cc6/Documents/Career/Website/rohanbpatel.github.io/portfolio_media/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohan\OneDrive\Documents\Career\Website\rohanbpatel.github.io\portfolio_media\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="6_{0272641C-0182-4F05-A401-33AAD6F775DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13093AF6-125B-4F3B-B917-E1CDB4926722}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D2B1511-E221-4B57-A031-0435A5B73D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="23226" windowHeight="13866" xr2:uid="{8903A9D0-2156-4902-9F33-57AFB774C556}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="43">
   <si>
     <t>https://www.robotevents.com/robot-competitions/vex-robotics-competition/RE-V5RC-24-7273.html#general-info</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>https://www.robotevents.com/robot-competitions/college-competition/RE-VURC-25-3390.html#general-info</t>
+  </si>
+  <si>
+    <t>https://events.vex.com/robot-competitions/vex-robotics-competition/RE-V5RC-26-4359.html#general-info</t>
+  </si>
+  <si>
+    <t>Speedway: Override VEX V5 Blended Signature Event</t>
   </si>
 </sst>
 </file>
@@ -534,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27EF56ED-11A2-47F1-8507-03A24103749B}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="60.64453125" customWidth="1"/>
@@ -562,47 +568,47 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2">
-        <v>46088</v>
+        <v>46283</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2">
-        <v>46027</v>
+        <v>46088</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
       </c>
       <c r="C4" s="2">
-        <v>45982</v>
+        <v>46027</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
@@ -613,33 +619,33 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2">
-        <v>45976</v>
+        <v>45982</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2">
-        <v>45724</v>
+        <v>45976</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>32</v>
@@ -647,13 +653,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C7" s="2">
-        <v>45675</v>
+        <v>45724</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
@@ -664,16 +670,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C8" s="2">
-        <v>45660</v>
+        <v>45675</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="E8" t="s">
         <v>32</v>
@@ -681,16 +687,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2">
-        <v>45633</v>
+        <v>45660</v>
       </c>
       <c r="D9" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
@@ -698,47 +704,47 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="C10" s="2">
-        <v>45618</v>
+        <v>45633</v>
       </c>
       <c r="D10" t="s">
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2">
-        <v>45346</v>
+        <v>45618</v>
       </c>
       <c r="D11" t="s">
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2">
-        <v>45311</v>
+        <v>45346</v>
       </c>
       <c r="D12" t="s">
         <v>19</v>
@@ -749,16 +755,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C13" s="2">
-        <v>45275</v>
+        <v>45311</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
@@ -766,16 +772,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2">
-        <v>45262</v>
+        <v>45275</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
         <v>32</v>
@@ -783,19 +789,19 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>44898</v>
+        <v>45262</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.5">
@@ -803,27 +809,27 @@
         <v>28</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C16" s="2">
-        <v>44534</v>
+        <v>44898</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2">
-        <v>44282</v>
+        <v>44534</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
@@ -832,9 +838,26 @@
         <v>32</v>
       </c>
     </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.5">
+      <c r="A18" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="2">
+        <v>44282</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E17">
-    <sortCondition descending="1" ref="C17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:E18">
+    <sortCondition descending="1" ref="C18"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
